--- a/docs/PlacementHub-Test-Cases-Delta-Post-Gen.xlsx
+++ b/docs/PlacementHub-Test-Cases-Delta-Post-Gen.xlsx
@@ -28,7 +28,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="9">
+  <fonts count="14">
     <font>
       <name val="Calibri"/>
       <family val="2"/>
@@ -79,8 +79,30 @@
       <b val="1"/>
       <sz val="10"/>
     </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="00006100"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <color rgb="009C0006"/>
+    </font>
+    <font>
+      <name val="Arial"/>
+      <b val="1"/>
+      <sz val="12"/>
+    </font>
   </fonts>
-  <fills count="6">
+  <fills count="8">
     <fill>
       <patternFill/>
     </fill>
@@ -107,8 +129,18 @@
         <fgColor rgb="00FEF9C3"/>
       </patternFill>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00C6EFCE"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="00FFC7CE"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="3">
+  <borders count="4">
     <border>
       <left/>
       <right/>
@@ -144,11 +176,25 @@
         <color rgb="00E2E8F0"/>
       </bottom>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="00D0D0D0"/>
+      </left>
+      <right style="thin">
+        <color rgb="00D0D0D0"/>
+      </right>
+      <top style="thin">
+        <color rgb="00D0D0D0"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00D0D0D0"/>
+      </bottom>
+    </border>
   </borders>
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="15">
+  <cellXfs count="21">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -177,6 +223,18 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="5" borderId="2" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="10" fillId="6" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="12" fillId="7" borderId="3" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment vertical="top" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
@@ -543,7 +601,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G13"/>
+  <dimension ref="A1:G34"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" min="1" max="1"/>
@@ -772,6 +830,189 @@
         <is>
           <t>CSV export: PlacementHub-Test-Cases-Delta-Post-Gen.csv (32 rows)</t>
         </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="15" t="inlineStr">
+        <is>
+          <t>Last automated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>Base URL</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>https://campus-placement-omega.vercel.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>Executed at</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:31:12.885Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B20" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" s="15" t="inlineStr">
+        <is>
+          <t>Last automated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>Base URL</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>https://campus-placement-omega.vercel.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>Executed at</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:33:43.239Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" s="15" t="inlineStr">
+        <is>
+          <t>Last automated run</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Base URL</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>https://campus-placement-omega.vercel.app</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Executed at</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:13.800Z</t>
+        </is>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>32</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>Fail</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>Blocked</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -801,7 +1042,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M13"/>
+  <dimension ref="A1:O13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -892,6 +1133,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>Executed At</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -958,7 +1209,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>ICS import 200: {"success":true,"imported":5,"duplicates":0,"skipped":0,"parsed":5,"calendarName":"PlacementHub Sample July 26","timezone":"Asia/Kolkata","preview":[{"title":"College Holiday Founders Day","startDate"</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:11.179Z</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -1023,7 +1288,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>Dry-run 200; clash/warnings: true {"success":true,"dryRun":true,"wouldImport":5,"skipped":0,"parsed":5,"calendarName":"PlacementHub Sample July 26","timezone":"Asia/Kolkata","preview":[{"title":"College Holiday Fou</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:11.934Z</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -1087,7 +1366,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Re-import ok; first={"success":true,"imported":0,"duplicates":5,"skipped":0,"parsed":5,"calendarName":"PlacementHub Samp second={"success":true,"imported":0,"duplicates":5,"skipped":0,"parsed":5,"calendarName":"PlacementHub Samp dupSafe=true</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:13.728Z</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -1146,7 +1439,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>Invalid ICS rejected (400): {"error":"File does not look like a valid .ics calendar. [Ref: B5DB96CA]","userMessage":"File does not look like a valid .ics calendar. [Ref: B5DB96CA]","refere</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:14.314Z</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -1212,7 +1519,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr"/>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>Export UI/API ok; month ICS=true status=200</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:17.235Z</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -1272,7 +1593,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr"/>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>Full ICS export contains imported Founders Day / sample UID</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:19.020Z</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -1338,7 +1673,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr"/>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>Delete imported range 200: {"success":true,"deleted":5,"fromDate":"2026-07-01","toDate":"2026-07-31","message":"Deleted 5 imported events."}</t>
+        </is>
+      </c>
+      <c r="O9" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:20.661Z</t>
+        </is>
+      </c>
     </row>
     <row r="10" ht="72" customHeight="1">
       <c r="A10" s="11" t="inlineStr">
@@ -1399,7 +1748,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr"/>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>Delete all imported 200: {"success":true,"deleted":5,"fromDate":null,"toDate":null,"message":"Deleted 5 imported events."}</t>
+        </is>
+      </c>
+      <c r="O10" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:22.795Z</t>
+        </is>
+      </c>
     </row>
     <row r="11" ht="72" customHeight="1">
       <c r="A11" s="11" t="inlineStr">
@@ -1464,7 +1827,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M11" s="11" t="inlineStr"/>
+      <c r="M11" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N11" s="18" t="inlineStr">
+        <is>
+          <t>Category filters present (count≈2)</t>
+        </is>
+      </c>
+      <c r="O11" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:24.160Z</t>
+        </is>
+      </c>
     </row>
     <row r="12" ht="72" customHeight="1">
       <c r="A12" s="11" t="inlineStr">
@@ -1528,7 +1905,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M12" s="11" t="inlineStr"/>
+      <c r="M12" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N12" s="18" t="inlineStr">
+        <is>
+          <t>Clash/imported warning surface detected (UI or dry-run payload)</t>
+        </is>
+      </c>
+      <c r="O12" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:25.923Z</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" s="11" t="inlineStr">
@@ -1588,7 +1979,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M13" s="11" t="inlineStr"/>
+      <c r="M13" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N13" s="18" t="inlineStr">
+        <is>
+          <t>Authz ok student=401 employer=401</t>
+        </is>
+      </c>
+      <c r="O13" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:28.002Z</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:M13"/>
@@ -1608,7 +2013,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M10"/>
+  <dimension ref="A1:O10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -1699,6 +2104,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>Executed At</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -1763,7 +2178,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>Feature Ideas loads; API 200 items=0</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:30.767Z</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -1825,7 +2254,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>Idea created 201; vote_count=1; id=3e532a25-5a26-4c69-a808-239113f0534a</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:31.496Z</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -1886,7 +2329,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Validation blocked no-topic=400 blank=400</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:32.632Z</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -1951,7 +2408,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t xml:space="preserve">Vote toggle 400/400: {"error":"Missing idea id [Ref: 8A3AC4D5]","userMessage":"Missing idea id [Ref:  | {"error":"Missing idea id [Ref: E71E7113]","userMessage":"Missing idea id [Ref: </t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:33.774Z</t>
+        </is>
+      </c>
     </row>
     <row r="7" ht="72" customHeight="1">
       <c r="A7" s="11" t="inlineStr">
@@ -2012,7 +2483,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr"/>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>Filters/API ok status=200</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:35.129Z</t>
+        </is>
+      </c>
     </row>
     <row r="8" ht="72" customHeight="1">
       <c r="A8" s="11" t="inlineStr">
@@ -2072,7 +2557,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M8" s="11" t="inlineStr"/>
+      <c r="M8" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N8" s="18" t="inlineStr">
+        <is>
+          <t>Sort APIs trending=200 newest=200; UI sort=true</t>
+        </is>
+      </c>
+      <c r="O8" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:38.953Z</t>
+        </is>
+      </c>
     </row>
     <row r="9" ht="72" customHeight="1">
       <c r="A9" s="11" t="inlineStr">
@@ -2136,7 +2635,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M9" s="11" t="inlineStr"/>
+      <c r="M9" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N9" s="18" t="inlineStr">
+        <is>
+          <t>API blocked student=401 employer=401; stu nav=https://campus-placement-omega.vercel.app/dashboard/student</t>
+        </is>
+      </c>
+      <c r="O9" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:40.439Z</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" s="11" t="inlineStr">
@@ -2195,7 +2708,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M10" s="11" t="inlineStr"/>
+      <c r="M10" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N10" s="18" t="inlineStr">
+        <is>
+          <t>Feature Ideas not in student/employer menus</t>
+        </is>
+      </c>
+      <c r="O10" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:41.803Z</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:M10"/>
@@ -2215,7 +2742,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2306,6 +2833,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>Executed At</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -2371,7 +2908,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>clear SQL deletes notifications; DB currently Alerts=0 (post prior clear)</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:43.470Z</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -2436,7 +2987,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>audit_logs wipe in SQL; current audit=0</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:44.970Z</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -2501,7 +3066,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Core campuses retained: bits-pilani, dtu-delhi, iiit-hyderabad, iit-madras, jadavpur-university, nit-trichy, vit-vellore</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:44:46.460Z</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -2565,7 +3144,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>Core logins ok; coreStudents=4</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:03.364Z</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -2625,7 +3218,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr"/>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>clear-placement script logs Alerts/Audit before/after style counts</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:03.365Z</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:M7"/>
@@ -2645,7 +3252,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M7"/>
+  <dimension ref="A1:O7"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -2736,6 +3343,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>Executed At</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -2800,7 +3417,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>Demo suffix visible; tenant=Indian Institute of Technology, Madras (Demo)</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:05.355Z</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -2864,7 +3495,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>Single Demo suffix: Indian Institute of Technology, Madras (Demo)</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:06.915Z</t>
+        </is>
+      </c>
     </row>
     <row r="5" ht="72" customHeight="1">
       <c r="A5" s="11" t="inlineStr">
@@ -2928,7 +3573,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Hub title/heading: title="PlacementHub — Campus Placement &amp; Engagement Platform" h1="Indian Institute of Technology, Madras (Demo) Home"</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:07.414Z</t>
+        </is>
+      </c>
     </row>
     <row r="6" ht="72" customHeight="1">
       <c r="A6" s="11" t="inlineStr">
@@ -2988,7 +3647,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M6" s="11" t="inlineStr"/>
+      <c r="M6" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N6" s="18" t="inlineStr">
+        <is>
+          <t>Student hub title="PlacementHub — Campus Placement &amp; Engagement Platform" h1="Arjun — Home"</t>
+        </is>
+      </c>
+      <c r="O6" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:08.284Z</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" s="11" t="inlineStr">
@@ -3052,7 +3725,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M7" s="11" t="inlineStr"/>
+      <c r="M7" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N7" s="18" t="inlineStr">
+        <is>
+          <t>Login demo chips include (Demo) labels after expanding Demo accounts</t>
+        </is>
+      </c>
+      <c r="O7" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:09.504Z</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:M7"/>
@@ -3072,7 +3759,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:M5"/>
+  <dimension ref="A1:O5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="12" customWidth="1" min="1" max="1"/>
@@ -3163,6 +3850,16 @@
           <t>Status</t>
         </is>
       </c>
+      <c r="N2" s="16" t="inlineStr">
+        <is>
+          <t>Actual Result</t>
+        </is>
+      </c>
+      <c r="O2" s="16" t="inlineStr">
+        <is>
+          <t>Executed At</t>
+        </is>
+      </c>
     </row>
     <row r="3" ht="72" customHeight="1">
       <c r="A3" s="11" t="inlineStr">
@@ -3228,7 +3925,21 @@
           <t>Candidate</t>
         </is>
       </c>
-      <c r="M3" s="11" t="inlineStr"/>
+      <c r="M3" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N3" s="18" t="inlineStr">
+        <is>
+          <t>Unlock page show/hide works; type after show=text</t>
+        </is>
+      </c>
+      <c r="O3" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:10.724Z</t>
+        </is>
+      </c>
     </row>
     <row r="4" ht="72" customHeight="1">
       <c r="A4" s="11" t="inlineStr">
@@ -3292,7 +4003,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M4" s="11" t="inlineStr"/>
+      <c r="M4" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N4" s="18" t="inlineStr">
+        <is>
+          <t>Unlock API ok; /developer reachable (https://campus-placement-omega.vercel.app/developer)</t>
+        </is>
+      </c>
+      <c r="O4" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:11.775Z</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="11" t="inlineStr">
@@ -3353,7 +4078,21 @@
           <t>Manual</t>
         </is>
       </c>
-      <c r="M5" s="11" t="inlineStr"/>
+      <c r="M5" s="17" t="inlineStr">
+        <is>
+          <t>Pass</t>
+        </is>
+      </c>
+      <c r="N5" s="18" t="inlineStr">
+        <is>
+          <t>Wrong password 401; developer still gated (https://campus-placement-omega.vercel.app/developer/unlock?from=%2Fdeveloper)</t>
+        </is>
+      </c>
+      <c r="O5" s="19" t="inlineStr">
+        <is>
+          <t>2026-07-21T17:45:12.815Z</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A2:M5"/>
